--- a/SaidaRPA/Excel/status-indicador_01-01-2026_31-01-2026.xlsx
+++ b/SaidaRPA/Excel/status-indicador_01-01-2026_31-01-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -541,7 +541,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CEA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -551,22 +551,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Novo</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CEA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risco a Imagem</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -581,32 +581,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CEEE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CEA</t>
+          <t>CEEE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -615,23 +615,23 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEA</t>
+          <t>CEEE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Imprensa | Favorabilidade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -646,16 +646,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -666,16 +666,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Análise</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -686,22 +686,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Imprensa | Favorabilidade</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>CSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -731,22 +731,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -755,18 +755,18 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Rechamadas</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CEEE</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
+          <t>Imprensa | Favorabilidade</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -811,22 +811,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CSA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -851,22 +851,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -875,23 +875,23 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Imprensa | Favorabilidade</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -901,52 +901,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>76</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -955,23 +955,23 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tratativas detratores</t>
+          <t>Redes Sociais | Menções Negativas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -981,27 +981,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Comportamento Inadequado</t>
+          <t>Fila INS Cliente</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Novo</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1011,22 +1011,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tempo excedido</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fila INS Cliente</t>
+          <t>Imprensa | Notícias de Impacto Negativo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1051,331 +1051,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Análise</t>
+          <t>Tempo excedido</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Análise</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Novo</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Redes Sociais | Menções Negativas</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Fila INS Cliente</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Análise</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tempo excedido</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Imprensa | Notícias de Impacto Negativo</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Tratativas detratores</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
